--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:40:18+00:00</t>
+    <t>2026-03-13T15:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:18:34+00:00</t>
+    <t>2026-03-13T15:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:51:21+00:00</t>
+    <t>2026-03-13T15:51:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:51:36+00:00</t>
+    <t>2026-03-13T16:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:06:25+00:00</t>
+    <t>2026-03-13T16:06:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:06:41+00:00</t>
+    <t>2026-03-13T16:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:06:55+00:00</t>
+    <t>2026-03-13T16:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T16:22:14+00:00</t>
+    <t>2026-06-26T11:49:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:49:40+00:00</t>
+    <t>2026-07-08T16:05:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
